--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B20F87B-36BB-0843-80E5-688CEF4414D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8828F316-1E44-434C-9408-18C349DB4A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="29920" windowHeight="14860" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -21938,7 +21938,7 @@
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6" t="s">
-        <v>2231</v>
+        <v>2255</v>
       </c>
       <c r="H56" s="13" t="s">
         <v>505</v>
@@ -23581,7 +23581,7 @@
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="10" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="H109" s="16" t="s">
         <v>506</v>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83636006-63C2-5F46-8F3A-95219841611C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFED02C-8B6D-FF47-AB61-7295C12DC242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="29920" windowHeight="14860" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -10407,7 +10407,7 @@
     <t>Prār;Säqă;Pälzäk;Ri;Ywār</t>
   </si>
   <si>
-    <t>wärză</t>
+    <t>wärz</t>
   </si>
 </sst>
 </file>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C850406D-2F42-D748-AC7E-ACBD3EC14E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCF7E3-D492-7D42-BFEC-12654684FFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2520" yWindow="580" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8089" uniqueCount="3479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8092" uniqueCount="3480">
   <si>
     <t>ID</t>
   </si>
@@ -10492,6 +10492,9 @@
   </si>
   <si>
     <t>Ugra</t>
+  </si>
+  <si>
+    <t>Sewā;Pälzäk</t>
   </si>
 </sst>
 </file>
@@ -49753,7 +49756,7 @@
       </c>
       <c r="F814" s="9"/>
       <c r="G814" s="9" t="s">
-        <v>3023</v>
+        <v>3479</v>
       </c>
       <c r="H814" s="6"/>
       <c r="I814" s="6"/>
@@ -56822,7 +56825,9 @@
         <v>2455</v>
       </c>
       <c r="F1131" s="6"/>
-      <c r="G1131" s="6"/>
+      <c r="G1131" s="6" t="s">
+        <v>2414</v>
+      </c>
       <c r="H1131" s="6"/>
       <c r="I1131" s="6"/>
       <c r="J1131" s="6"/>
@@ -56958,7 +56963,9 @@
         <v>2455</v>
       </c>
       <c r="F1137" s="6"/>
-      <c r="G1137" s="6"/>
+      <c r="G1137" s="6" t="s">
+        <v>2414</v>
+      </c>
       <c r="H1137" s="6"/>
       <c r="I1137" s="6"/>
       <c r="J1137" s="6"/>
@@ -58184,7 +58191,9 @@
         <v>2455</v>
       </c>
       <c r="F1191" s="9"/>
-      <c r="G1191" s="6"/>
+      <c r="G1191" s="6" t="s">
+        <v>2414</v>
+      </c>
       <c r="H1191" s="6"/>
       <c r="I1191" s="6"/>
       <c r="J1191" s="6"/>
@@ -68910,6 +68919,9 @@
       </c>
     </row>
     <row r="1677" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1677" s="6">
+        <v>1745</v>
+      </c>
       <c r="B1677" s="1" t="s">
         <v>3458</v>
       </c>
@@ -68927,6 +68939,9 @@
       </c>
     </row>
     <row r="1678" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1678" s="6">
+        <v>1746</v>
+      </c>
       <c r="B1678" s="1" t="s">
         <v>3460</v>
       </c>
@@ -68944,6 +68959,9 @@
       </c>
     </row>
     <row r="1679" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1679" s="6">
+        <v>1747</v>
+      </c>
       <c r="B1679" s="1" t="s">
         <v>3462</v>
       </c>
@@ -68961,6 +68979,9 @@
       </c>
     </row>
     <row r="1680" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1680" s="6">
+        <v>1748</v>
+      </c>
       <c r="B1680" s="1" t="s">
         <v>3464</v>
       </c>
@@ -68971,7 +68992,10 @@
         <v>32</v>
       </c>
     </row>
-    <row r="1681" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1681" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1681" s="6">
+        <v>1749</v>
+      </c>
       <c r="B1681" s="1" t="s">
         <v>3466</v>
       </c>
@@ -68988,7 +69012,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1682" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1682" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1682" s="6">
+        <v>1750</v>
+      </c>
       <c r="B1682" s="1" t="s">
         <v>3467</v>
       </c>
@@ -69002,7 +69029,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1683" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1683" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1683" s="6">
+        <v>1751</v>
+      </c>
       <c r="B1683" s="1" t="s">
         <v>391</v>
       </c>
@@ -69019,7 +69049,10 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="1684" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1684" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1684" s="6">
+        <v>1752</v>
+      </c>
       <c r="B1684" s="1" t="s">
         <v>3470</v>
       </c>
@@ -69033,7 +69066,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1685" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1685" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1685" s="6">
+        <v>1753</v>
+      </c>
       <c r="B1685" s="1" t="s">
         <v>3472</v>
       </c>
@@ -69047,7 +69083,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1686" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1686" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1686" s="6">
+        <v>1754</v>
+      </c>
       <c r="B1686" s="1" t="s">
         <v>3474</v>
       </c>
@@ -69061,7 +69100,10 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="1687" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1687" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1687" s="6">
+        <v>1755</v>
+      </c>
       <c r="B1687" s="1" t="s">
         <v>3475</v>
       </c>
@@ -69078,7 +69120,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="1688" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1688" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1688" s="6">
+        <v>1756</v>
+      </c>
       <c r="B1688" s="1" t="s">
         <v>3477</v>
       </c>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCF7E3-D492-7D42-BFEC-12654684FFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEED0331-D7B6-154B-834A-933EE9C1DCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="580" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
+    <workbookView xWindow="2500" yWindow="580" windowWidth="29920" windowHeight="10340" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Inflection" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8092" uniqueCount="3480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8131" uniqueCount="3498">
   <si>
     <t>ID</t>
   </si>
@@ -10495,6 +10495,60 @@
   </si>
   <si>
     <t>Sewā;Pälzäk</t>
+  </si>
+  <si>
+    <t>uttaragorav</t>
+  </si>
+  <si>
+    <t>Uttaragaurava</t>
+  </si>
+  <si>
+    <t>utpatti</t>
+  </si>
+  <si>
+    <t>origin</t>
+  </si>
+  <si>
+    <t>uddeśake</t>
+  </si>
+  <si>
+    <t>director</t>
+  </si>
+  <si>
+    <t>unmatte</t>
+  </si>
+  <si>
+    <t>insane</t>
+  </si>
+  <si>
+    <t>upage</t>
+  </si>
+  <si>
+    <t>Upaga</t>
+  </si>
+  <si>
+    <t>upadeś</t>
+  </si>
+  <si>
+    <t>instruction</t>
+  </si>
+  <si>
+    <t>upādān</t>
+  </si>
+  <si>
+    <t>clinging</t>
+  </si>
+  <si>
+    <t>uri</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>urbilwā`</t>
+  </si>
+  <si>
+    <t>Urubilvā</t>
   </si>
 </sst>
 </file>
@@ -12233,7 +12287,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE25BEAE-ECB0-3E42-A39B-2C15C3BB1FB8}">
-  <dimension ref="A1:XFB1688"/>
+  <dimension ref="A1:XFB1697"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -38187,7 +38241,9 @@
       </c>
       <c r="E327" s="6"/>
       <c r="F327" s="8"/>
-      <c r="G327" s="8"/>
+      <c r="G327" s="6" t="s">
+        <v>2420</v>
+      </c>
       <c r="H327" s="6"/>
       <c r="I327" s="6"/>
       <c r="J327" s="6"/>
@@ -69096,9 +69152,6 @@
       <c r="D1686" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1686" s="1" t="s">
-        <v>2455</v>
-      </c>
     </row>
     <row r="1687" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1687" s="6">
@@ -69113,9 +69166,6 @@
       <c r="D1687" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1687" s="1" t="s">
-        <v>2455</v>
-      </c>
       <c r="F1687" s="1" t="s">
         <v>27</v>
       </c>
@@ -69137,6 +69187,171 @@
         <v>18</v>
       </c>
       <c r="F1688" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1689" s="6">
+        <v>1757</v>
+      </c>
+      <c r="B1689" s="1" t="s">
+        <v>3480</v>
+      </c>
+      <c r="C1689" s="1" t="s">
+        <v>3481</v>
+      </c>
+      <c r="D1689" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1689" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1689" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1690" s="6">
+        <v>1758</v>
+      </c>
+      <c r="B1690" s="1" t="s">
+        <v>3482</v>
+      </c>
+      <c r="C1690" s="1" t="s">
+        <v>3483</v>
+      </c>
+      <c r="D1690" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1690" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1691" s="6">
+        <v>1759</v>
+      </c>
+      <c r="B1691" s="1" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C1691" s="1" t="s">
+        <v>3485</v>
+      </c>
+      <c r="D1691" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E1691" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1691" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1692" s="6">
+        <v>1760</v>
+      </c>
+      <c r="B1692" s="1" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C1692" s="1" t="s">
+        <v>3487</v>
+      </c>
+      <c r="D1692" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1692" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1693" s="6">
+        <v>1761</v>
+      </c>
+      <c r="B1693" s="1" t="s">
+        <v>3488</v>
+      </c>
+      <c r="C1693" s="1" t="s">
+        <v>3489</v>
+      </c>
+      <c r="D1693" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E1693" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1693" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1694" s="6">
+        <v>1762</v>
+      </c>
+      <c r="B1694" s="1" t="s">
+        <v>3490</v>
+      </c>
+      <c r="C1694" s="1" t="s">
+        <v>3491</v>
+      </c>
+      <c r="D1694" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1694" s="1" t="s">
+        <v>2455</v>
+      </c>
+      <c r="F1694" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1695" s="6">
+        <v>1763</v>
+      </c>
+      <c r="B1695" s="1" t="s">
+        <v>3492</v>
+      </c>
+      <c r="C1695" s="1" t="s">
+        <v>3493</v>
+      </c>
+      <c r="D1695" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1695" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1696" s="6">
+        <v>1764</v>
+      </c>
+      <c r="B1696" s="1" t="s">
+        <v>3494</v>
+      </c>
+      <c r="C1696" s="1" t="s">
+        <v>3495</v>
+      </c>
+      <c r="D1696" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="F1696" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1697" s="6">
+        <v>1765</v>
+      </c>
+      <c r="B1697" s="1" t="s">
+        <v>3496</v>
+      </c>
+      <c r="C1697" s="1" t="s">
+        <v>3497</v>
+      </c>
+      <c r="D1697" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1697" s="1" t="s">
         <v>27</v>
       </c>
     </row>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEED0331-D7B6-154B-834A-933EE9C1DCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BE454B-099C-2742-87E3-9AC883EBACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2500" yWindow="580" windowWidth="29920" windowHeight="10340" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
+    <workbookView xWindow="2500" yWindow="580" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Inflection" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8131" uniqueCount="3498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8134" uniqueCount="3500">
   <si>
     <t>ID</t>
   </si>
@@ -10549,6 +10549,12 @@
   </si>
   <si>
     <t>Urubilvā</t>
+  </si>
+  <si>
+    <t>enṣke</t>
+  </si>
+  <si>
+    <t>while</t>
   </si>
 </sst>
 </file>
@@ -12287,7 +12293,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE25BEAE-ECB0-3E42-A39B-2C15C3BB1FB8}">
-  <dimension ref="A1:XFB1697"/>
+  <dimension ref="A1:XFB1698"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -69355,6 +69361,17 @@
         <v>27</v>
       </c>
     </row>
+    <row r="1698" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1698" s="1" t="s">
+        <v>3498</v>
+      </c>
+      <c r="C1698" s="1" t="s">
+        <v>3499</v>
+      </c>
+      <c r="D1698" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K280">
     <sortCondition ref="A273:A280"/>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BE454B-099C-2742-87E3-9AC883EBACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7F6480-D25C-F845-9541-1140558751B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2500" yWindow="580" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
+    <workbookView xWindow="3580" yWindow="2720" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Inflection" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8134" uniqueCount="3500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8143" uniqueCount="3505">
   <si>
     <t>ID</t>
   </si>
@@ -10555,6 +10555,21 @@
   </si>
   <si>
     <t>while</t>
+  </si>
+  <si>
+    <t>ek</t>
+  </si>
+  <si>
+    <t>fodder</t>
+  </si>
+  <si>
+    <t>enākă</t>
+  </si>
+  <si>
+    <t>ehe</t>
+  </si>
+  <si>
+    <t>āās</t>
   </si>
 </sst>
 </file>
@@ -12293,7 +12308,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE25BEAE-ECB0-3E42-A39B-2C15C3BB1FB8}">
-  <dimension ref="A1:XFB1698"/>
+  <dimension ref="A1:XFB1701"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -69096,7 +69111,7 @@
         <v>1751</v>
       </c>
       <c r="B1683" s="1" t="s">
-        <v>391</v>
+        <v>3504</v>
       </c>
       <c r="C1683" s="1" t="s">
         <v>3469</v>
@@ -69369,6 +69384,39 @@
         <v>3499</v>
       </c>
       <c r="D1698" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1699" s="1" t="s">
+        <v>3500</v>
+      </c>
+      <c r="C1699" s="1" t="s">
+        <v>3501</v>
+      </c>
+      <c r="D1699" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1700" s="1" t="s">
+        <v>3502</v>
+      </c>
+      <c r="C1700" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1700" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1701" s="1" t="s">
+        <v>3503</v>
+      </c>
+      <c r="C1701" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="D1701" s="1" t="s">
         <v>32</v>
       </c>
     </row>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7F6480-D25C-F845-9541-1140558751B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6659D00F-865B-EA48-8244-F9E4420625E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3580" yWindow="2720" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -10569,7 +10569,7 @@
     <t>ehe</t>
   </si>
   <si>
-    <t>āās</t>
+    <t>ā``s</t>
   </si>
 </sst>
 </file>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6659D00F-865B-EA48-8244-F9E4420625E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053A82C2-1DB3-3345-83CB-63659280B36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3580" yWindow="2720" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
+    <workbookView xWindow="3800" yWindow="580" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Inflection" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8143" uniqueCount="3505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8145" uniqueCount="3505">
   <si>
     <t>ID</t>
   </si>
@@ -12265,9 +12265,7 @@
         <v>32</v>
       </c>
       <c r="E33" s="6"/>
-      <c r="F33" s="6" t="s">
-        <v>2926</v>
-      </c>
+      <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
@@ -12308,7 +12306,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE25BEAE-ECB0-3E42-A39B-2C15C3BB1FB8}">
-  <dimension ref="A1:XFB1701"/>
+  <dimension ref="A1:XFB1702"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -69377,6 +69375,9 @@
       </c>
     </row>
     <row r="1698" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1698" s="6">
+        <v>1766</v>
+      </c>
       <c r="B1698" s="1" t="s">
         <v>3498</v>
       </c>
@@ -69388,6 +69389,9 @@
       </c>
     </row>
     <row r="1699" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1699" s="6">
+        <v>1767</v>
+      </c>
       <c r="B1699" s="1" t="s">
         <v>3500</v>
       </c>
@@ -69399,6 +69403,9 @@
       </c>
     </row>
     <row r="1700" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1700" s="6">
+        <v>1768</v>
+      </c>
       <c r="B1700" s="1" t="s">
         <v>3502</v>
       </c>
@@ -69410,6 +69417,9 @@
       </c>
     </row>
     <row r="1701" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1701" s="6">
+        <v>1769</v>
+      </c>
       <c r="B1701" s="1" t="s">
         <v>3503</v>
       </c>
@@ -69418,6 +69428,20 @@
       </c>
       <c r="D1701" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1702" s="6">
+        <v>1770</v>
+      </c>
+      <c r="B1702" s="1" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C1702" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D1702" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B567BD1F-CDFD-6B43-8C33-67FD8BAC0F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CBF3E5-C264-364C-9BCD-31A0151E9654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8146" uniqueCount="3506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8149" uniqueCount="3507">
   <si>
     <t>ID</t>
   </si>
@@ -10573,6 +10573,9 @@
   </si>
   <si>
     <t>nikṣātr</t>
+  </si>
+  <si>
+    <t>tuṭă</t>
   </si>
 </sst>
 </file>
@@ -12309,7 +12312,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE25BEAE-ECB0-3E42-A39B-2C15C3BB1FB8}">
-  <dimension ref="A1:XFB1702"/>
+  <dimension ref="A1:XFB1703"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" customWidth="1"/>
@@ -69449,6 +69452,20 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1703" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1703" s="6">
+        <v>1771</v>
+      </c>
+      <c r="B1703" s="1" t="s">
+        <v>3506</v>
+      </c>
+      <c r="C1703" s="1" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D1703" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K280">
     <sortCondition ref="A273:A280"/>

--- a/data/morphemes.xlsx
+++ b/data/morphemes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergeimalyshev/Desktop/Tocharian/Tocharian A/My grammar/Candrakanta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960C6D91-65E9-4E42-AE3B-0E0D18164D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC64EAD6-D358-E148-BEBD-E2DF1BD7FC99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="580" windowWidth="29920" windowHeight="10340" activeTab="2" xr2:uid="{DFFD3512-190B-6C44-A03E-FE8C03207A6B}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8174" uniqueCount="3516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8175" uniqueCount="3516">
   <si>
     <t>ID</t>
   </si>
@@ -58227,7 +58227,9 @@
       <c r="D1188" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E1188" s="9"/>
+      <c r="E1188" s="9" t="s">
+        <v>2451</v>
+      </c>
       <c r="F1188" s="9"/>
       <c r="G1188" s="6" t="s">
         <v>2410</v>
